--- a/docs/downloads/20260903_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260903_Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AM20"/>
+  <dimension ref="A2:AP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,10 @@
     <col width="9" customWidth="1" min="36" max="36"/>
     <col width="9" customWidth="1" min="37" max="37"/>
     <col width="9" customWidth="1" min="38" max="38"/>
-    <col width="46" customWidth="1" min="39" max="39"/>
+    <col width="9" customWidth="1" min="39" max="39"/>
+    <col width="9" customWidth="1" min="40" max="40"/>
+    <col width="9" customWidth="1" min="41" max="41"/>
+    <col width="46" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -581,8 +584,11 @@
       <c r="AG3" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AJ3" s="3" t="n">
         <v>46262</v>
+      </c>
+      <c r="AM3" s="4" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -763,22 +769,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AJ4" s="6" t="inlineStr">
+      <c r="AJ4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AK4" s="6" t="inlineStr">
+      <c r="AK4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AL4" s="6" t="inlineStr">
+      <c r="AL4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AM4" s="5" t="inlineStr">
+      <c r="AM4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AN4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AO4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AP4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -828,6 +849,9 @@
       <c r="AK5" s="8" t="n"/>
       <c r="AL5" s="8" t="n"/>
       <c r="AM5" s="8" t="n"/>
+      <c r="AN5" s="8" t="n"/>
+      <c r="AO5" s="8" t="n"/>
+      <c r="AP5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -956,20 +980,31 @@
         <f>AH6/$D$6</f>
         <v/>
       </c>
-      <c r="AJ6" s="14">
+      <c r="AJ6" s="12">
         <f>AK6-AH6</f>
         <v/>
       </c>
-      <c r="AK6" s="14" t="n">
+      <c r="AK6" s="12" t="n">
         <v>307</v>
       </c>
-      <c r="AL6" s="15">
+      <c r="AL6" s="13">
         <f>AK6/$D$6</f>
         <v/>
       </c>
-      <c r="AM6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 191 units, Block B: 116 units</t>
+      <c r="AM6" s="14">
+        <f>AN6-AK6</f>
+        <v/>
+      </c>
+      <c r="AN6" s="14" t="n">
+        <v>310</v>
+      </c>
+      <c r="AO6" s="15">
+        <f>AN6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AP6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 193 units, Block B: 117 units</t>
         </is>
       </c>
     </row>
@@ -1100,20 +1135,31 @@
         <f>AH7/$D$7</f>
         <v/>
       </c>
-      <c r="AJ7" s="14">
+      <c r="AJ7" s="12">
         <f>AK7-AH7</f>
         <v/>
       </c>
-      <c r="AK7" s="14" t="n">
+      <c r="AK7" s="12" t="n">
         <v>972</v>
       </c>
-      <c r="AL7" s="15">
+      <c r="AL7" s="13">
         <f>AK7/$D$7</f>
         <v/>
       </c>
-      <c r="AM7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 400 units, Block B: 376 units, Block C: 87 units, Block D: 109 units</t>
+      <c r="AM7" s="14">
+        <f>AN7-AK7</f>
+        <v/>
+      </c>
+      <c r="AN7" s="14" t="n">
+        <v>975</v>
+      </c>
+      <c r="AO7" s="15">
+        <f>AN7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AP7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 400 units, Block B: 377 units, Block C: 89 units, Block D: 109 units</t>
         </is>
       </c>
     </row>
@@ -1244,18 +1290,29 @@
         <f>AH8/$D$8</f>
         <v/>
       </c>
-      <c r="AJ8" s="14">
+      <c r="AJ8" s="12">
         <f>AK8-AH8</f>
         <v/>
       </c>
-      <c r="AK8" s="14" t="n">
+      <c r="AK8" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="AL8" s="15">
+      <c r="AL8" s="13">
         <f>AK8/$D$8</f>
         <v/>
       </c>
-      <c r="AM8" s="10" t="inlineStr">
+      <c r="AM8" s="14">
+        <f>AN8-AK8</f>
+        <v/>
+      </c>
+      <c r="AN8" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO8" s="15">
+        <f>AN8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AP8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1388,20 +1445,31 @@
         <f>AH9/$D$9</f>
         <v/>
       </c>
-      <c r="AJ9" s="14">
+      <c r="AJ9" s="12">
         <f>AK9-AH9</f>
         <v/>
       </c>
-      <c r="AK9" s="14" t="n">
+      <c r="AK9" s="12" t="n">
         <v>1062</v>
       </c>
-      <c r="AL9" s="15">
+      <c r="AL9" s="13">
         <f>AK9/$D$9</f>
         <v/>
       </c>
-      <c r="AM9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 667 units, Phase 2: 395 units</t>
+      <c r="AM9" s="14">
+        <f>AN9-AK9</f>
+        <v/>
+      </c>
+      <c r="AN9" s="14" t="n">
+        <v>1068</v>
+      </c>
+      <c r="AO9" s="15">
+        <f>AN9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AP9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 668 units, Phase 2: 400 units</t>
         </is>
       </c>
     </row>
@@ -1449,6 +1517,9 @@
       <c r="AK10" s="8" t="n"/>
       <c r="AL10" s="8" t="n"/>
       <c r="AM10" s="8" t="n"/>
+      <c r="AN10" s="8" t="n"/>
+      <c r="AO10" s="8" t="n"/>
+      <c r="AP10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1577,18 +1648,29 @@
         <f>AH11/$D$11</f>
         <v/>
       </c>
-      <c r="AJ11" s="14">
+      <c r="AJ11" s="12">
         <f>AK11-AH11</f>
         <v/>
       </c>
-      <c r="AK11" s="14" t="n">
+      <c r="AK11" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="AL11" s="15">
+      <c r="AL11" s="13">
         <f>AK11/$D$11</f>
         <v/>
       </c>
-      <c r="AM11" s="10" t="inlineStr">
+      <c r="AM11" s="14">
+        <f>AN11-AK11</f>
+        <v/>
+      </c>
+      <c r="AN11" s="14" t="n">
+        <v>845</v>
+      </c>
+      <c r="AO11" s="15">
+        <f>AN11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AP11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1721,20 +1803,31 @@
         <f>AH12/$D$12</f>
         <v/>
       </c>
-      <c r="AJ12" s="14">
+      <c r="AJ12" s="12">
         <f>AK12-AH12</f>
         <v/>
       </c>
-      <c r="AK12" s="14" t="n">
+      <c r="AK12" s="12" t="n">
         <v>1497</v>
       </c>
-      <c r="AL12" s="15">
+      <c r="AL12" s="13">
         <f>AK12/$D$12</f>
         <v/>
       </c>
-      <c r="AM12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 493 units, Block B: 531 units, Block D: 473 units</t>
+      <c r="AM12" s="14">
+        <f>AN12-AK12</f>
+        <v/>
+      </c>
+      <c r="AN12" s="14" t="n">
+        <v>1503</v>
+      </c>
+      <c r="AO12" s="15">
+        <f>AN12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AP12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 497 units, Block B: 531 units, Block D: 475 units</t>
         </is>
       </c>
     </row>
@@ -1865,20 +1958,31 @@
         <f>AH13/$D$13</f>
         <v/>
       </c>
-      <c r="AJ13" s="14">
+      <c r="AJ13" s="12">
         <f>AK13-AH13</f>
         <v/>
       </c>
-      <c r="AK13" s="14" t="n">
+      <c r="AK13" s="12" t="n">
         <v>1006</v>
       </c>
-      <c r="AL13" s="15">
+      <c r="AL13" s="13">
         <f>AK13/$D$13</f>
         <v/>
       </c>
-      <c r="AM13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 403 units, Block B: 369 units, Block C: 234 units</t>
+      <c r="AM13" s="14">
+        <f>AN13-AK13</f>
+        <v/>
+      </c>
+      <c r="AN13" s="14" t="n">
+        <v>1011</v>
+      </c>
+      <c r="AO13" s="15">
+        <f>AN13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AP13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 403 units, Block B: 371 units, Block C: 237 units</t>
         </is>
       </c>
     </row>
@@ -2009,20 +2113,31 @@
         <f>AH14/$D$14</f>
         <v/>
       </c>
-      <c r="AJ14" s="14">
+      <c r="AJ14" s="12">
         <f>AK14-AH14</f>
         <v/>
       </c>
-      <c r="AK14" s="14" t="n">
+      <c r="AK14" s="12" t="n">
         <v>756</v>
       </c>
-      <c r="AL14" s="15">
+      <c r="AL14" s="13">
         <f>AK14/$D$14</f>
         <v/>
       </c>
-      <c r="AM14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 499 units, Block B: 257 units</t>
+      <c r="AM14" s="14">
+        <f>AN14-AK14</f>
+        <v/>
+      </c>
+      <c r="AN14" s="14" t="n">
+        <v>762</v>
+      </c>
+      <c r="AO14" s="15">
+        <f>AN14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AP14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 501 units, Block B: 261 units</t>
         </is>
       </c>
     </row>
@@ -2153,20 +2268,31 @@
         <f>AH15/$D$15</f>
         <v/>
       </c>
-      <c r="AJ15" s="14">
+      <c r="AJ15" s="12">
         <f>AK15-AH15</f>
         <v/>
       </c>
-      <c r="AK15" s="14" t="n">
+      <c r="AK15" s="12" t="n">
         <v>1396</v>
       </c>
-      <c r="AL15" s="15">
+      <c r="AL15" s="13">
         <f>AK15/$D$15</f>
         <v/>
       </c>
-      <c r="AM15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 728 units, Block B: 668 units</t>
+      <c r="AM15" s="14">
+        <f>AN15-AK15</f>
+        <v/>
+      </c>
+      <c r="AN15" s="14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AO15" s="15">
+        <f>AN15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AP15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 728 units, Block B: 672 units</t>
         </is>
       </c>
     </row>
@@ -2297,18 +2423,29 @@
         <f>AH16/$D$16</f>
         <v/>
       </c>
-      <c r="AJ16" s="14">
+      <c r="AJ16" s="12">
         <f>AK16-AH16</f>
         <v/>
       </c>
-      <c r="AK16" s="14" t="n">
+      <c r="AK16" s="12" t="n">
         <v>908</v>
       </c>
-      <c r="AL16" s="15">
+      <c r="AL16" s="13">
         <f>AK16/$D$16</f>
         <v/>
       </c>
-      <c r="AM16" s="10" t="inlineStr">
+      <c r="AM16" s="14">
+        <f>AN16-AK16</f>
+        <v/>
+      </c>
+      <c r="AN16" s="14" t="n">
+        <v>908</v>
+      </c>
+      <c r="AO16" s="15">
+        <f>AN16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2423,10 +2560,13 @@
       <c r="AG17" s="12" t="n"/>
       <c r="AH17" s="12" t="n"/>
       <c r="AI17" s="13" t="n"/>
-      <c r="AJ17" s="14" t="n"/>
-      <c r="AK17" s="14" t="n"/>
-      <c r="AL17" s="15" t="n"/>
-      <c r="AM17" s="10" t="inlineStr">
+      <c r="AJ17" s="12" t="n"/>
+      <c r="AK17" s="12" t="n"/>
+      <c r="AL17" s="13" t="n"/>
+      <c r="AM17" s="14" t="n"/>
+      <c r="AN17" s="14" t="n"/>
+      <c r="AO17" s="15" t="n"/>
+      <c r="AP17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -2559,20 +2699,31 @@
         <f>AH18/$D$18</f>
         <v/>
       </c>
-      <c r="AJ18" s="14">
+      <c r="AJ18" s="12">
         <f>AK18-AH18</f>
         <v/>
       </c>
-      <c r="AK18" s="14" t="n">
+      <c r="AK18" s="12" t="n">
         <v>725</v>
       </c>
-      <c r="AL18" s="15">
+      <c r="AL18" s="13">
         <f>AK18/$D$18</f>
         <v/>
       </c>
-      <c r="AM18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 439 units, Block B: 286 units</t>
+      <c r="AM18" s="14">
+        <f>AN18-AK18</f>
+        <v/>
+      </c>
+      <c r="AN18" s="14" t="n">
+        <v>727</v>
+      </c>
+      <c r="AO18" s="15">
+        <f>AN18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AP18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 440 units, Block B: 287 units</t>
         </is>
       </c>
     </row>
@@ -2703,20 +2854,31 @@
         <f>AH19/$D$19</f>
         <v/>
       </c>
-      <c r="AJ19" s="14">
+      <c r="AJ19" s="12">
         <f>AK19-AH19</f>
         <v/>
       </c>
-      <c r="AK19" s="14" t="n">
+      <c r="AK19" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="AL19" s="15">
+      <c r="AL19" s="13">
         <f>AK19/$D$19</f>
         <v/>
       </c>
-      <c r="AM19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 297 units, Block B: 93 units</t>
+      <c r="AM19" s="14">
+        <f>AN19-AK19</f>
+        <v/>
+      </c>
+      <c r="AN19" s="14" t="n">
+        <v>393</v>
+      </c>
+      <c r="AO19" s="15">
+        <f>AN19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AP19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 297 units, Block B: 96 units</t>
         </is>
       </c>
     </row>
@@ -2847,25 +3009,36 @@
         <f>AH20/$D$20</f>
         <v/>
       </c>
-      <c r="AJ20" s="14">
+      <c r="AJ20" s="12">
         <f>AK20-AH20</f>
         <v/>
       </c>
-      <c r="AK20" s="14" t="n">
+      <c r="AK20" s="12" t="n">
         <v>306</v>
       </c>
-      <c r="AL20" s="15">
+      <c r="AL20" s="13">
         <f>AK20/$D$20</f>
         <v/>
       </c>
-      <c r="AM20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 215 units, Block B: 91 units</t>
+      <c r="AM20" s="14">
+        <f>AN20-AK20</f>
+        <v/>
+      </c>
+      <c r="AN20" s="14" t="n">
+        <v>314</v>
+      </c>
+      <c r="AO20" s="15">
+        <f>AN20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AP20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 219 units, Block B: 95 units</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>
@@ -2877,6 +3050,7 @@
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="AM3:AO3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
